--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>83000</v>
+        <v>83100</v>
       </c>
       <c r="C419" t="n">
-        <v>64610</v>
+        <v>111095</v>
       </c>
       <c r="D419" t="n">
-        <v>77976</v>
+        <v>78065</v>
       </c>
       <c r="E419" t="n">
-        <v>81445</v>
+        <v>81498</v>
       </c>
       <c r="F419" t="n">
-        <v>84202</v>
+        <v>84070</v>
       </c>
       <c r="G419" t="n">
-        <v>81208</v>
+        <v>81211</v>
       </c>
       <c r="H419" t="n">
-        <v>-0.001364994650696616</v>
+        <v>-0.001328102903380479</v>
       </c>
     </row>
   </sheetData>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>-0.001328102903380479</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>83600</v>
+      </c>
+      <c r="C420" t="n">
+        <v>25409</v>
+      </c>
+      <c r="D420" t="n">
+        <v>78362</v>
+      </c>
+      <c r="E420" t="n">
+        <v>82025</v>
+      </c>
+      <c r="F420" t="n">
+        <v>83423</v>
+      </c>
+      <c r="G420" t="n">
+        <v>81270</v>
+      </c>
+      <c r="H420" t="n">
+        <v>-0.000602565206163419</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>83200</v>
+        <v>83400</v>
       </c>
       <c r="C421" t="n">
-        <v>2600</v>
+        <v>36406</v>
       </c>
       <c r="D421" t="n">
-        <v>78481</v>
+        <v>78542</v>
       </c>
       <c r="E421" t="n">
-        <v>82027</v>
+        <v>82058</v>
       </c>
       <c r="F421" t="n">
-        <v>83273</v>
+        <v>83291</v>
       </c>
       <c r="G421" t="n">
-        <v>81260</v>
+        <v>81297</v>
       </c>
       <c r="H421" t="n">
-        <v>-0.0007255376972171712</v>
+        <v>-0.0002705394803182992</v>
       </c>
     </row>
   </sheetData>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>-0.0002705394803182992</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>83300</v>
+      </c>
+      <c r="C422" t="n">
+        <v>34600</v>
+      </c>
+      <c r="D422" t="n">
+        <v>78710</v>
+      </c>
+      <c r="E422" t="n">
+        <v>82086</v>
+      </c>
+      <c r="F422" t="n">
+        <v>83365</v>
+      </c>
+      <c r="G422" t="n">
+        <v>81387</v>
+      </c>
+      <c r="H422" t="n">
+        <v>0.0008362129391654705</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>0.0008362129391654705</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>83300</v>
+      </c>
+      <c r="C423" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D423" t="n">
+        <v>79243</v>
+      </c>
+      <c r="E423" t="n">
+        <v>81919</v>
+      </c>
+      <c r="F423" t="n">
+        <v>83264</v>
+      </c>
+      <c r="G423" t="n">
+        <v>81476</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0.001930668109543898</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>0.001930668109543898</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>83500</v>
+      </c>
+      <c r="C424" t="n">
+        <v>73658</v>
+      </c>
+      <c r="D424" t="n">
+        <v>79638</v>
+      </c>
+      <c r="E424" t="n">
+        <v>82003</v>
+      </c>
+      <c r="F424" t="n">
+        <v>83397</v>
+      </c>
+      <c r="G424" t="n">
+        <v>81679</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0.004427009677935079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>0.004427009677935079</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>82600</v>
+      </c>
+      <c r="C425" t="n">
+        <v>48790</v>
+      </c>
+      <c r="D425" t="n">
+        <v>80386</v>
+      </c>
+      <c r="E425" t="n">
+        <v>82034</v>
+      </c>
+      <c r="F425" t="n">
+        <v>83246</v>
+      </c>
+      <c r="G425" t="n">
+        <v>81889</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0.007009431990063764</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>0.007009431990063764</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>83200</v>
+      </c>
+      <c r="C426" t="n">
+        <v>39444</v>
+      </c>
+      <c r="D426" t="n">
+        <v>80431</v>
+      </c>
+      <c r="E426" t="n">
+        <v>82091</v>
+      </c>
+      <c r="F426" t="n">
+        <v>83221</v>
+      </c>
+      <c r="G426" t="n">
+        <v>81914</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.007316863217698311</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>83100</v>
+      </c>
+      <c r="C427" t="n">
+        <v>55025</v>
+      </c>
+      <c r="D427" t="n">
+        <v>80488</v>
+      </c>
+      <c r="E427" t="n">
+        <v>82341</v>
+      </c>
+      <c r="F427" t="n">
+        <v>83191</v>
+      </c>
+      <c r="G427" t="n">
+        <v>82007</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0.008460507384498106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>0.008460507384498106</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>84700</v>
+      </c>
+      <c r="C428" t="n">
+        <v>53768</v>
+      </c>
+      <c r="D428" t="n">
+        <v>81209</v>
+      </c>
+      <c r="E428" t="n">
+        <v>82617</v>
+      </c>
+      <c r="F428" t="n">
+        <v>83451</v>
+      </c>
+      <c r="G428" t="n">
+        <v>82426</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0.01361305475965024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>0.01361305475965024</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>83800</v>
+      </c>
+      <c r="C429" t="n">
+        <v>134869</v>
+      </c>
+      <c r="D429" t="n">
+        <v>81408</v>
+      </c>
+      <c r="E429" t="n">
+        <v>82846</v>
+      </c>
+      <c r="F429" t="n">
+        <v>83582</v>
+      </c>
+      <c r="G429" t="n">
+        <v>82612</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0.01590034309325006</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>0.01590034309325006</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>84200</v>
+      </c>
+      <c r="C430" t="n">
+        <v>60508</v>
+      </c>
+      <c r="D430" t="n">
+        <v>81474</v>
+      </c>
+      <c r="E430" t="n">
+        <v>83057</v>
+      </c>
+      <c r="F430" t="n">
+        <v>83830</v>
+      </c>
+      <c r="G430" t="n">
+        <v>82787</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0.01805236168669078</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>0.01805236168669078</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>86300</v>
+      </c>
+      <c r="C431" t="n">
+        <v>79658</v>
+      </c>
+      <c r="D431" t="n">
+        <v>81963</v>
+      </c>
+      <c r="E431" t="n">
+        <v>83924</v>
+      </c>
+      <c r="F431" t="n">
+        <v>84408</v>
+      </c>
+      <c r="G431" t="n">
+        <v>83432</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0.02598408735965774</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>0.02598408735965774</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>87000</v>
+      </c>
+      <c r="C432" t="n">
+        <v>56164</v>
+      </c>
+      <c r="D432" t="n">
+        <v>82184</v>
+      </c>
+      <c r="E432" t="n">
+        <v>84076</v>
+      </c>
+      <c r="F432" t="n">
+        <v>84973</v>
+      </c>
+      <c r="G432" t="n">
+        <v>83744</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0.02982082908053463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>0.02982082908053463</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>85700</v>
+      </c>
+      <c r="C433" t="n">
+        <v>73969</v>
+      </c>
+      <c r="D433" t="n">
+        <v>82350</v>
+      </c>
+      <c r="E433" t="n">
+        <v>84042</v>
+      </c>
+      <c r="F433" t="n">
+        <v>85142</v>
+      </c>
+      <c r="G433" t="n">
+        <v>83845</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0.0310628512401776</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>0.0310628512401776</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>97600</v>
+      </c>
+      <c r="C434" t="n">
+        <v>299135</v>
+      </c>
+      <c r="D434" t="n">
+        <v>83974</v>
+      </c>
+      <c r="E434" t="n">
+        <v>87008</v>
+      </c>
+      <c r="F434" t="n">
+        <v>92004</v>
+      </c>
+      <c r="G434" t="n">
+        <v>87662</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.07800145107539436</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>0.07800145107539436</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>97500</v>
+      </c>
+      <c r="C435" t="n">
+        <v>196822</v>
+      </c>
+      <c r="D435" t="n">
+        <v>84860</v>
+      </c>
+      <c r="E435" t="n">
+        <v>88492</v>
+      </c>
+      <c r="F435" t="n">
+        <v>94206</v>
+      </c>
+      <c r="G435" t="n">
+        <v>89186</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.09674245871198606</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>0.09674245871198606</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>97600</v>
+      </c>
+      <c r="C436" t="n">
+        <v>266994</v>
+      </c>
+      <c r="D436" t="n">
+        <v>86171</v>
+      </c>
+      <c r="E436" t="n">
+        <v>90452</v>
+      </c>
+      <c r="F436" t="n">
+        <v>95926</v>
+      </c>
+      <c r="G436" t="n">
+        <v>90850</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0.1172050812233303</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>0.1172050812233303</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>97300</v>
+      </c>
+      <c r="C437" t="n">
+        <v>127219</v>
+      </c>
+      <c r="D437" t="n">
+        <v>86783</v>
+      </c>
+      <c r="E437" t="n">
+        <v>90946</v>
+      </c>
+      <c r="F437" t="n">
+        <v>96627</v>
+      </c>
+      <c r="G437" t="n">
+        <v>91452</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0.1246080251847661</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>0.1246080251847661</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>97100</v>
+      </c>
+      <c r="C438" t="n">
+        <v>77389</v>
+      </c>
+      <c r="D438" t="n">
+        <v>87157</v>
+      </c>
+      <c r="E438" t="n">
+        <v>91312</v>
+      </c>
+      <c r="F438" t="n">
+        <v>97500</v>
+      </c>
+      <c r="G438" t="n">
+        <v>91990</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.131223945203458</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>0.131223945203458</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>96700</v>
+      </c>
+      <c r="C439" t="n">
+        <v>126496</v>
+      </c>
+      <c r="D439" t="n">
+        <v>87511</v>
+      </c>
+      <c r="E439" t="n">
+        <v>91821</v>
+      </c>
+      <c r="F439" t="n">
+        <v>97335</v>
+      </c>
+      <c r="G439" t="n">
+        <v>92222</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.1340769069959049</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>0.1340769069959049</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>96000</v>
+      </c>
+      <c r="C440" t="n">
+        <v>215062</v>
+      </c>
+      <c r="D440" t="n">
+        <v>88015</v>
+      </c>
+      <c r="E440" t="n">
+        <v>92394</v>
+      </c>
+      <c r="F440" t="n">
+        <v>96942</v>
+      </c>
+      <c r="G440" t="n">
+        <v>92450</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.1368806797919306</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>0.1368806797919306</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>93300</v>
+      </c>
+      <c r="C441" t="n">
+        <v>119411</v>
+      </c>
+      <c r="D441" t="n">
+        <v>88444</v>
+      </c>
+      <c r="E441" t="n">
+        <v>92443</v>
+      </c>
+      <c r="F441" t="n">
+        <v>96025</v>
+      </c>
+      <c r="G441" t="n">
+        <v>92304</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.1350852814225458</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>0.1350852814225458</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>95300</v>
+      </c>
+      <c r="C442" t="n">
+        <v>76370</v>
+      </c>
+      <c r="D442" t="n">
+        <v>88714</v>
+      </c>
+      <c r="E442" t="n">
+        <v>92539</v>
+      </c>
+      <c r="F442" t="n">
+        <v>95671</v>
+      </c>
+      <c r="G442" t="n">
+        <v>92308</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.1351344704189672</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>0.1351344704189672</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>95100</v>
+      </c>
+      <c r="C443" t="n">
+        <v>100274</v>
+      </c>
+      <c r="D443" t="n">
+        <v>88994</v>
+      </c>
+      <c r="E443" t="n">
+        <v>93053</v>
+      </c>
+      <c r="F443" t="n">
+        <v>95408</v>
+      </c>
+      <c r="G443" t="n">
+        <v>92485</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0.1373110835106186</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>0.1373110835106186</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>96300</v>
+      </c>
+      <c r="C444" t="n">
+        <v>41532</v>
+      </c>
+      <c r="D444" t="n">
+        <v>89078</v>
+      </c>
+      <c r="E444" t="n">
+        <v>93426</v>
+      </c>
+      <c r="F444" t="n">
+        <v>95179</v>
+      </c>
+      <c r="G444" t="n">
+        <v>92561</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0.1382456744426273</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/에스원_일별_기준주가.xlsx
+++ b/data/에스원_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>0.1382456744426273</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>97700</v>
+      </c>
+      <c r="C445" t="n">
+        <v>98395</v>
+      </c>
+      <c r="D445" t="n">
+        <v>89305</v>
+      </c>
+      <c r="E445" t="n">
+        <v>93839</v>
+      </c>
+      <c r="F445" t="n">
+        <v>95343</v>
+      </c>
+      <c r="G445" t="n">
+        <v>92829</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0.1415413372028678</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
